--- a/Excel/EquipSpeicalConfig.xlsx
+++ b/Excel/EquipSpeicalConfig.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
-    <sheet name="定制装备" sheetId="4" r:id="rId1"/>
+    <sheet name="四格" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="31">
   <si>
     <t>#</t>
   </si>
@@ -36,6 +36,12 @@
   </si>
   <si>
     <t>Sid</t>
+  </si>
+  <si>
+    <t>Part</t>
+  </si>
+  <si>
+    <t>Quality</t>
   </si>
   <si>
     <t>Name</t>
@@ -1085,36 +1091,36 @@
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.4166666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5416666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="27.5833333333333" style="2" customWidth="1"/>
-    <col min="9" max="9" width="20.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.8166666666667" style="2" customWidth="1"/>
-    <col min="11" max="16369" width="9" style="2"/>
-    <col min="16370" max="16384" width="9" style="1"/>
+    <col min="3" max="6" width="9.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.4166666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5416666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="27.5833333333333" style="2" customWidth="1"/>
+    <col min="11" max="11" width="20.25" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.8166666666667" style="2" customWidth="1"/>
+    <col min="13" max="16371" width="9" style="2"/>
+    <col min="16372" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:11 16370:16384">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="K1" s="1" t="s">
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="M1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:11 16370:16384">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="K2" s="1" t="s">
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="M2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:11 16370:16384">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1141,12 +1147,18 @@
       <c r="J3" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:11 16370:16384">
+      <c r="K3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -1169,178 +1181,218 @@
       <c r="J4" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:11 16370:16384">
+      <c r="K4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:11 16370:16384">
+        <v>14</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="4">
+      <c r="E6" s="1">
+        <v>1001</v>
+      </c>
+      <c r="F6" s="1">
+        <v>3</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="4">
         <v>0</v>
       </c>
-      <c r="G6" s="4">
+      <c r="I6" s="4">
         <v>5</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="J6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:11 16370:16384">
+      <c r="K6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1">
         <v>2</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="4">
+      <c r="E7" s="1">
+        <v>1002</v>
+      </c>
+      <c r="F7" s="1">
+        <v>3</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="4">
         <v>0</v>
       </c>
-      <c r="G7" s="4">
+      <c r="I7" s="4">
         <v>5</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="J7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:11 16370:16384">
+      <c r="K7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="1">
+        <v>1003</v>
+      </c>
+      <c r="F8" s="1">
+        <v>3</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>5</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="4">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4">
-        <v>5</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:11 16370:16384">
+      <c r="L8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1">
         <v>4</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="E9" s="1">
+        <v>1004</v>
+      </c>
+      <c r="F9" s="1">
+        <v>3</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="4">
         <v>0</v>
       </c>
-      <c r="G9" s="4">
+      <c r="I9" s="4">
         <v>5</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="J9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:11 16370:16384">
+      <c r="K9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:13 16372:16384">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="4">
+      <c r="E10" s="1">
+        <v>1001</v>
+      </c>
+      <c r="F10" s="1">
+        <v>4</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="4">
         <v>6</v>
       </c>
-      <c r="G10" s="4">
+      <c r="I10" s="4">
         <v>10</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="J10" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="XEP10" s="1"/>
-      <c r="XEQ10" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="XER10" s="1"/>
       <c r="XES10" s="1"/>
       <c r="XET10" s="1"/>
@@ -1355,33 +1407,37 @@
       <c r="XFC10" s="1"/>
       <c r="XFD10" s="1"/>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:11 16370:16384">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:13 16372:16384">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1">
         <v>2</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="4">
+      <c r="E11" s="1">
+        <v>1002</v>
+      </c>
+      <c r="F11" s="1">
+        <v>4</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="4">
         <v>6</v>
       </c>
-      <c r="G11" s="4">
+      <c r="I11" s="4">
         <v>10</v>
       </c>
-      <c r="H11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="J11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="XEP11" s="1"/>
-      <c r="XEQ11" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="XER11" s="1"/>
       <c r="XES11" s="1"/>
       <c r="XET11" s="1"/>
@@ -1396,33 +1452,37 @@
       <c r="XFC11" s="1"/>
       <c r="XFD11" s="1"/>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:11 16370:16384">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:13 16372:16384">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1">
         <v>3</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="1">
+        <v>1003</v>
+      </c>
+      <c r="F12" s="1">
+        <v>4</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="4">
+        <v>6</v>
+      </c>
+      <c r="I12" s="4">
+        <v>10</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="4">
-        <v>6</v>
-      </c>
-      <c r="G12" s="4">
-        <v>10</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="XEP12" s="1"/>
-      <c r="XEQ12" s="1"/>
+      <c r="L12" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="XER12" s="1"/>
       <c r="XES12" s="1"/>
       <c r="XET12" s="1"/>
@@ -1437,33 +1497,37 @@
       <c r="XFC12" s="1"/>
       <c r="XFD12" s="1"/>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:11 16370:16384">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:13 16372:16384">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1">
         <v>4</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="4">
+      <c r="E13" s="1">
+        <v>1004</v>
+      </c>
+      <c r="F13" s="1">
+        <v>4</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="4">
         <v>6</v>
       </c>
-      <c r="G13" s="4">
+      <c r="I13" s="4">
         <v>10</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="J13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="XEP13" s="1"/>
-      <c r="XEQ13" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="XER13" s="1"/>
       <c r="XES13" s="1"/>
       <c r="XET13" s="1"/>
@@ -1478,17 +1542,17 @@
       <c r="XFC13" s="1"/>
       <c r="XFD13" s="1"/>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:11 16370:16384">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:13 16372:16384">
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
       <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
       <c r="J14" s="1"/>
-      <c r="XEP14" s="1"/>
-      <c r="XEQ14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
       <c r="XER14" s="1"/>
       <c r="XES14" s="1"/>
       <c r="XET14" s="1"/>
@@ -1503,17 +1567,17 @@
       <c r="XFC14" s="1"/>
       <c r="XFD14" s="1"/>
     </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:11 16370:16384">
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:13 16372:16384">
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
       <c r="J15" s="1"/>
-      <c r="XEP15" s="1"/>
-      <c r="XEQ15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
       <c r="XER15" s="1"/>
       <c r="XES15" s="1"/>
       <c r="XET15" s="1"/>
@@ -1528,17 +1592,17 @@
       <c r="XFC15" s="1"/>
       <c r="XFD15" s="1"/>
     </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:11 16370:16384">
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:13 16372:16384">
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
       <c r="G16" s="4"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
       <c r="J16" s="1"/>
-      <c r="XEP16" s="1"/>
-      <c r="XEQ16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
       <c r="XER16" s="1"/>
       <c r="XES16" s="1"/>
       <c r="XET16" s="1"/>
@@ -1553,17 +1617,17 @@
       <c r="XFC16" s="1"/>
       <c r="XFD16" s="1"/>
     </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:10 16370:16384">
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
       <c r="G17" s="4"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
       <c r="J17" s="1"/>
-      <c r="XEP17" s="1"/>
-      <c r="XEQ17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
       <c r="XER17" s="1"/>
       <c r="XES17" s="1"/>
       <c r="XET17" s="1"/>
@@ -1578,17 +1642,17 @@
       <c r="XFC17" s="1"/>
       <c r="XFD17" s="1"/>
     </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:10 16370:16384">
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
       <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
       <c r="J18" s="1"/>
-      <c r="XEP18" s="1"/>
-      <c r="XEQ18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
       <c r="XER18" s="1"/>
       <c r="XES18" s="1"/>
       <c r="XET18" s="1"/>
@@ -1603,17 +1667,17 @@
       <c r="XFC18" s="1"/>
       <c r="XFD18" s="1"/>
     </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:10 16370:16384">
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
       <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
       <c r="J19" s="1"/>
-      <c r="XEP19" s="1"/>
-      <c r="XEQ19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
       <c r="XER19" s="1"/>
       <c r="XES19" s="1"/>
       <c r="XET19" s="1"/>
@@ -1628,17 +1692,17 @@
       <c r="XFC19" s="1"/>
       <c r="XFD19" s="1"/>
     </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:10 16370:16384">
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
       <c r="G20" s="4"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
       <c r="J20" s="1"/>
-      <c r="XEP20" s="1"/>
-      <c r="XEQ20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
       <c r="XER20" s="1"/>
       <c r="XES20" s="1"/>
       <c r="XET20" s="1"/>
@@ -1653,17 +1717,17 @@
       <c r="XFC20" s="1"/>
       <c r="XFD20" s="1"/>
     </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:10 16370:16384">
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
       <c r="J21" s="1"/>
-      <c r="XEP21" s="1"/>
-      <c r="XEQ21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
       <c r="XER21" s="1"/>
       <c r="XES21" s="1"/>
       <c r="XET21" s="1"/>
@@ -1678,17 +1742,17 @@
       <c r="XFC21" s="1"/>
       <c r="XFD21" s="1"/>
     </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:10 16370:16384">
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
       <c r="J22" s="1"/>
-      <c r="XEP22" s="1"/>
-      <c r="XEQ22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
       <c r="XER22" s="1"/>
       <c r="XES22" s="1"/>
       <c r="XET22" s="1"/>
@@ -1703,17 +1767,17 @@
       <c r="XFC22" s="1"/>
       <c r="XFD22" s="1"/>
     </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:10 16370:16384">
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
       <c r="G23" s="4"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
       <c r="J23" s="1"/>
-      <c r="XEP23" s="1"/>
-      <c r="XEQ23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
       <c r="XER23" s="1"/>
       <c r="XES23" s="1"/>
       <c r="XET23" s="1"/>
@@ -1728,17 +1792,17 @@
       <c r="XFC23" s="1"/>
       <c r="XFD23" s="1"/>
     </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:10 16370:16384">
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
       <c r="G24" s="4"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
       <c r="J24" s="1"/>
-      <c r="XEP24" s="1"/>
-      <c r="XEQ24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
       <c r="XER24" s="1"/>
       <c r="XES24" s="1"/>
       <c r="XET24" s="1"/>
@@ -1753,17 +1817,17 @@
       <c r="XFC24" s="1"/>
       <c r="XFD24" s="1"/>
     </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:10 16370:16384">
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
       <c r="G25" s="4"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
       <c r="J25" s="1"/>
-      <c r="XEP25" s="1"/>
-      <c r="XEQ25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
       <c r="XER25" s="1"/>
       <c r="XES25" s="1"/>
       <c r="XET25" s="1"/>
@@ -1778,7 +1842,7 @@
       <c r="XFC25" s="1"/>
       <c r="XFD25" s="1"/>
     </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:10 16370:16384">
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -1786,8 +1850,8 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-      <c r="XEP26" s="1"/>
-      <c r="XEQ26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
       <c r="XER26" s="1"/>
       <c r="XES26" s="1"/>
       <c r="XET26" s="1"/>
@@ -1802,7 +1866,7 @@
       <c r="XFC26" s="1"/>
       <c r="XFD26" s="1"/>
     </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:10 16370:16384">
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -1810,8 +1874,8 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="XEP27" s="1"/>
-      <c r="XEQ27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
       <c r="XER27" s="1"/>
       <c r="XES27" s="1"/>
       <c r="XET27" s="1"/>
@@ -1826,7 +1890,7 @@
       <c r="XFC27" s="1"/>
       <c r="XFD27" s="1"/>
     </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:10 16370:16384">
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -1834,8 +1898,8 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-      <c r="XEP28" s="1"/>
-      <c r="XEQ28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
       <c r="XER28" s="1"/>
       <c r="XES28" s="1"/>
       <c r="XET28" s="1"/>
@@ -1850,7 +1914,7 @@
       <c r="XFC28" s="1"/>
       <c r="XFD28" s="1"/>
     </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:10 16370:16384">
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -1858,8 +1922,8 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-      <c r="XEP29" s="1"/>
-      <c r="XEQ29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
       <c r="XER29" s="1"/>
       <c r="XES29" s="1"/>
       <c r="XET29" s="1"/>
@@ -1874,7 +1938,7 @@
       <c r="XFC29" s="1"/>
       <c r="XFD29" s="1"/>
     </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:10 16370:16384">
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -1882,8 +1946,8 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-      <c r="XEP30" s="1"/>
-      <c r="XEQ30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
       <c r="XER30" s="1"/>
       <c r="XES30" s="1"/>
       <c r="XET30" s="1"/>
@@ -1898,7 +1962,7 @@
       <c r="XFC30" s="1"/>
       <c r="XFD30" s="1"/>
     </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:10 16370:16384">
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -1906,8 +1970,8 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
-      <c r="XEP31" s="1"/>
-      <c r="XEQ31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
       <c r="XER31" s="1"/>
       <c r="XES31" s="1"/>
       <c r="XET31" s="1"/>
@@ -1922,7 +1986,7 @@
       <c r="XFC31" s="1"/>
       <c r="XFD31" s="1"/>
     </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:10 16370:16384">
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -1930,8 +1994,8 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
-      <c r="XEP32" s="1"/>
-      <c r="XEQ32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
       <c r="XER32" s="1"/>
       <c r="XES32" s="1"/>
       <c r="XET32" s="1"/>
@@ -1946,7 +2010,7 @@
       <c r="XFC32" s="1"/>
       <c r="XFD32" s="1"/>
     </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -1954,8 +2018,8 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
-      <c r="XEP33" s="1"/>
-      <c r="XEQ33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
       <c r="XER33" s="1"/>
       <c r="XES33" s="1"/>
       <c r="XET33" s="1"/>
@@ -1970,7 +2034,7 @@
       <c r="XFC33" s="1"/>
       <c r="XFD33" s="1"/>
     </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -1978,8 +2042,8 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
-      <c r="XEP34" s="1"/>
-      <c r="XEQ34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
       <c r="XER34" s="1"/>
       <c r="XES34" s="1"/>
       <c r="XET34" s="1"/>
@@ -1994,7 +2058,7 @@
       <c r="XFC34" s="1"/>
       <c r="XFD34" s="1"/>
     </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -2002,8 +2066,8 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
-      <c r="XEP35" s="1"/>
-      <c r="XEQ35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
       <c r="XER35" s="1"/>
       <c r="XES35" s="1"/>
       <c r="XET35" s="1"/>
@@ -2018,7 +2082,7 @@
       <c r="XFC35" s="1"/>
       <c r="XFD35" s="1"/>
     </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -2026,8 +2090,8 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
-      <c r="XEP36" s="1"/>
-      <c r="XEQ36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
       <c r="XER36" s="1"/>
       <c r="XES36" s="1"/>
       <c r="XET36" s="1"/>
@@ -2042,7 +2106,7 @@
       <c r="XFC36" s="1"/>
       <c r="XFD36" s="1"/>
     </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -2050,8 +2114,8 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
-      <c r="XEP37" s="1"/>
-      <c r="XEQ37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
       <c r="XER37" s="1"/>
       <c r="XES37" s="1"/>
       <c r="XET37" s="1"/>
@@ -2066,7 +2130,7 @@
       <c r="XFC37" s="1"/>
       <c r="XFD37" s="1"/>
     </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -2074,8 +2138,8 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
-      <c r="XEP38" s="1"/>
-      <c r="XEQ38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
       <c r="XER38" s="1"/>
       <c r="XES38" s="1"/>
       <c r="XET38" s="1"/>
@@ -2090,7 +2154,7 @@
       <c r="XFC38" s="1"/>
       <c r="XFD38" s="1"/>
     </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -2098,8 +2162,8 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
-      <c r="XEP39" s="1"/>
-      <c r="XEQ39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
       <c r="XER39" s="1"/>
       <c r="XES39" s="1"/>
       <c r="XET39" s="1"/>
@@ -2114,7 +2178,7 @@
       <c r="XFC39" s="1"/>
       <c r="XFD39" s="1"/>
     </row>
-    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -2122,8 +2186,8 @@
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
-      <c r="XEP40" s="1"/>
-      <c r="XEQ40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
       <c r="XER40" s="1"/>
       <c r="XES40" s="1"/>
       <c r="XET40" s="1"/>
@@ -2138,7 +2202,7 @@
       <c r="XFC40" s="1"/>
       <c r="XFD40" s="1"/>
     </row>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -2146,8 +2210,8 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="XEP41" s="1"/>
-      <c r="XEQ41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
       <c r="XER41" s="1"/>
       <c r="XES41" s="1"/>
       <c r="XET41" s="1"/>
@@ -2162,7 +2226,7 @@
       <c r="XFC41" s="1"/>
       <c r="XFD41" s="1"/>
     </row>
-    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -2170,8 +2234,8 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="XEP42" s="1"/>
-      <c r="XEQ42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
       <c r="XER42" s="1"/>
       <c r="XES42" s="1"/>
       <c r="XET42" s="1"/>
@@ -2186,7 +2250,7 @@
       <c r="XFC42" s="1"/>
       <c r="XFD42" s="1"/>
     </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -2194,8 +2258,8 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
-      <c r="XEP43" s="1"/>
-      <c r="XEQ43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
       <c r="XER43" s="1"/>
       <c r="XES43" s="1"/>
       <c r="XET43" s="1"/>
@@ -2210,7 +2274,7 @@
       <c r="XFC43" s="1"/>
       <c r="XFD43" s="1"/>
     </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -2218,8 +2282,8 @@
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-      <c r="XEP44" s="1"/>
-      <c r="XEQ44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
       <c r="XER44" s="1"/>
       <c r="XES44" s="1"/>
       <c r="XET44" s="1"/>
@@ -2234,7 +2298,7 @@
       <c r="XFC44" s="1"/>
       <c r="XFD44" s="1"/>
     </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -2242,8 +2306,8 @@
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
-      <c r="XEP46" s="1"/>
-      <c r="XEQ46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
       <c r="XER46" s="1"/>
       <c r="XES46" s="1"/>
       <c r="XET46" s="1"/>
@@ -2258,7 +2322,7 @@
       <c r="XFC46" s="1"/>
       <c r="XFD46" s="1"/>
     </row>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -2266,8 +2330,8 @@
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
-      <c r="XEP47" s="1"/>
-      <c r="XEQ47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
       <c r="XER47" s="1"/>
       <c r="XES47" s="1"/>
       <c r="XET47" s="1"/>
@@ -2282,7 +2346,7 @@
       <c r="XFC47" s="1"/>
       <c r="XFD47" s="1"/>
     </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -2290,8 +2354,8 @@
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
-      <c r="XEP48" s="1"/>
-      <c r="XEQ48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
       <c r="XER48" s="1"/>
       <c r="XES48" s="1"/>
       <c r="XET48" s="1"/>
@@ -2306,7 +2370,7 @@
       <c r="XFC48" s="1"/>
       <c r="XFD48" s="1"/>
     </row>
-    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -2314,8 +2378,8 @@
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
-      <c r="XEP49" s="1"/>
-      <c r="XEQ49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
       <c r="XER49" s="1"/>
       <c r="XES49" s="1"/>
       <c r="XET49" s="1"/>
@@ -2330,7 +2394,7 @@
       <c r="XFC49" s="1"/>
       <c r="XFD49" s="1"/>
     </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -2338,8 +2402,8 @@
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
-      <c r="XEP50" s="1"/>
-      <c r="XEQ50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
       <c r="XER50" s="1"/>
       <c r="XES50" s="1"/>
       <c r="XET50" s="1"/>
@@ -2354,7 +2418,7 @@
       <c r="XFC50" s="1"/>
       <c r="XFD50" s="1"/>
     </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -2362,8 +2426,8 @@
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
-      <c r="XEP51" s="1"/>
-      <c r="XEQ51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
       <c r="XER51" s="1"/>
       <c r="XES51" s="1"/>
       <c r="XET51" s="1"/>
@@ -2378,7 +2442,7 @@
       <c r="XFC51" s="1"/>
       <c r="XFD51" s="1"/>
     </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -2386,8 +2450,8 @@
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
-      <c r="XEP52" s="1"/>
-      <c r="XEQ52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
       <c r="XER52" s="1"/>
       <c r="XES52" s="1"/>
       <c r="XET52" s="1"/>
@@ -2402,7 +2466,7 @@
       <c r="XFC52" s="1"/>
       <c r="XFD52" s="1"/>
     </row>
-    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -2410,8 +2474,8 @@
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-      <c r="XEP53" s="1"/>
-      <c r="XEQ53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
       <c r="XER53" s="1"/>
       <c r="XES53" s="1"/>
       <c r="XET53" s="1"/>
@@ -2426,7 +2490,7 @@
       <c r="XFC53" s="1"/>
       <c r="XFD53" s="1"/>
     </row>
-    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -2434,8 +2498,8 @@
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-      <c r="XEP54" s="1"/>
-      <c r="XEQ54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
       <c r="XER54" s="1"/>
       <c r="XES54" s="1"/>
       <c r="XET54" s="1"/>
@@ -2450,7 +2514,7 @@
       <c r="XFC54" s="1"/>
       <c r="XFD54" s="1"/>
     </row>
-    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -2458,8 +2522,8 @@
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
-      <c r="XEP55" s="1"/>
-      <c r="XEQ55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
       <c r="XER55" s="1"/>
       <c r="XES55" s="1"/>
       <c r="XET55" s="1"/>
@@ -2474,7 +2538,7 @@
       <c r="XFC55" s="1"/>
       <c r="XFD55" s="1"/>
     </row>
-    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -2482,8 +2546,8 @@
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
-      <c r="XEP56" s="1"/>
-      <c r="XEQ56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
       <c r="XER56" s="1"/>
       <c r="XES56" s="1"/>
       <c r="XET56" s="1"/>
@@ -2498,7 +2562,7 @@
       <c r="XFC56" s="1"/>
       <c r="XFD56" s="1"/>
     </row>
-    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -2506,8 +2570,8 @@
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
-      <c r="XEP57" s="1"/>
-      <c r="XEQ57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
       <c r="XER57" s="1"/>
       <c r="XES57" s="1"/>
       <c r="XET57" s="1"/>
@@ -2522,7 +2586,7 @@
       <c r="XFC57" s="1"/>
       <c r="XFD57" s="1"/>
     </row>
-    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -2530,8 +2594,8 @@
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
-      <c r="XEP58" s="1"/>
-      <c r="XEQ58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
       <c r="XER58" s="1"/>
       <c r="XES58" s="1"/>
       <c r="XET58" s="1"/>
@@ -2546,7 +2610,7 @@
       <c r="XFC58" s="1"/>
       <c r="XFD58" s="1"/>
     </row>
-    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -2554,8 +2618,8 @@
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
-      <c r="XEP59" s="1"/>
-      <c r="XEQ59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
       <c r="XER59" s="1"/>
       <c r="XES59" s="1"/>
       <c r="XET59" s="1"/>
@@ -2570,7 +2634,7 @@
       <c r="XFC59" s="1"/>
       <c r="XFD59" s="1"/>
     </row>
-    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -2578,8 +2642,8 @@
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
-      <c r="XEP60" s="1"/>
-      <c r="XEQ60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
       <c r="XER60" s="1"/>
       <c r="XES60" s="1"/>
       <c r="XET60" s="1"/>
@@ -2594,7 +2658,7 @@
       <c r="XFC60" s="1"/>
       <c r="XFD60" s="1"/>
     </row>
-    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -2602,8 +2666,8 @@
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
-      <c r="XEP61" s="1"/>
-      <c r="XEQ61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
       <c r="XER61" s="1"/>
       <c r="XES61" s="1"/>
       <c r="XET61" s="1"/>
@@ -2618,7 +2682,7 @@
       <c r="XFC61" s="1"/>
       <c r="XFD61" s="1"/>
     </row>
-    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -2626,8 +2690,8 @@
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
-      <c r="XEP62" s="1"/>
-      <c r="XEQ62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
       <c r="XER62" s="1"/>
       <c r="XES62" s="1"/>
       <c r="XET62" s="1"/>
@@ -2642,7 +2706,7 @@
       <c r="XFC62" s="1"/>
       <c r="XFD62" s="1"/>
     </row>
-    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -2650,8 +2714,8 @@
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
-      <c r="XEP63" s="1"/>
-      <c r="XEQ63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
       <c r="XER63" s="1"/>
       <c r="XES63" s="1"/>
       <c r="XET63" s="1"/>
@@ -2666,7 +2730,7 @@
       <c r="XFC63" s="1"/>
       <c r="XFD63" s="1"/>
     </row>
-    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -2674,8 +2738,8 @@
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
-      <c r="XEP64" s="1"/>
-      <c r="XEQ64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
       <c r="XER64" s="1"/>
       <c r="XES64" s="1"/>
       <c r="XET64" s="1"/>
@@ -2690,7 +2754,7 @@
       <c r="XFC64" s="1"/>
       <c r="XFD64" s="1"/>
     </row>
-    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -2698,8 +2762,8 @@
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
-      <c r="XEP65" s="1"/>
-      <c r="XEQ65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
       <c r="XER65" s="1"/>
       <c r="XES65" s="1"/>
       <c r="XET65" s="1"/>
@@ -2714,7 +2778,7 @@
       <c r="XFC65" s="1"/>
       <c r="XFD65" s="1"/>
     </row>
-    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:9 16370:16384">
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -2722,8 +2786,8 @@
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
-      <c r="XEP66" s="1"/>
-      <c r="XEQ66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
       <c r="XER66" s="1"/>
       <c r="XES66" s="1"/>
       <c r="XET66" s="1"/>
@@ -2740,7 +2804,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J3 C4:E4 F4 G4 H4:I4 J4 C5:I5 J5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5 F3:L5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipSpeicalConfig.xlsx
+++ b/Excel/EquipSpeicalConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="33">
   <si>
     <t>#</t>
   </si>
@@ -36,6 +36,12 @@
   </si>
   <si>
     <t>Sid</t>
+  </si>
+  <si>
+    <t>Cycle</t>
+  </si>
+  <si>
+    <t>LevelRequired</t>
   </si>
   <si>
     <t>Part</t>
@@ -1091,36 +1097,36 @@
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="6" width="9.875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.4166666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5416666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="27.5833333333333" style="2" customWidth="1"/>
-    <col min="11" max="11" width="20.25" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.8166666666667" style="2" customWidth="1"/>
-    <col min="13" max="16371" width="9" style="2"/>
-    <col min="16372" max="16384" width="9" style="1"/>
+    <col min="3" max="8" width="9.875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.4166666666667" style="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5416666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="27.5833333333333" style="2" customWidth="1"/>
+    <col min="13" max="13" width="20.25" style="2" customWidth="1"/>
+    <col min="14" max="14" width="18.8166666666667" style="2" customWidth="1"/>
+    <col min="15" max="16373" width="9" style="2"/>
+    <col min="16374" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="M1" s="1" t="s">
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="O1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="M2" s="1" t="s">
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="O2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1153,12 +1159,18 @@
       <c r="L3" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+      <c r="M3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -1187,42 +1199,54 @@
       <c r="L4" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+      <c r="M4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+        <v>16</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1230,34 +1254,40 @@
         <v>1</v>
       </c>
       <c r="E6" s="1">
+        <v>101</v>
+      </c>
+      <c r="F6" s="1">
+        <v>10</v>
+      </c>
+      <c r="G6" s="1">
         <v>1001</v>
       </c>
-      <c r="F6" s="1">
+      <c r="H6" s="1">
         <v>3</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="4">
+      <c r="I6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="4">
         <v>0</v>
       </c>
-      <c r="I6" s="4">
+      <c r="K6" s="4">
         <v>5</v>
       </c>
-      <c r="J6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="L6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M6" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+      <c r="M6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1265,34 +1295,40 @@
         <v>2</v>
       </c>
       <c r="E7" s="1">
+        <v>101</v>
+      </c>
+      <c r="F7" s="1">
+        <v>10</v>
+      </c>
+      <c r="G7" s="1">
         <v>1002</v>
       </c>
-      <c r="F7" s="1">
+      <c r="H7" s="1">
         <v>3</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="4">
+      <c r="I7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="4">
         <v>0</v>
       </c>
-      <c r="I7" s="4">
+      <c r="K7" s="4">
         <v>5</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="L7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M7" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+      <c r="M7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1300,34 +1336,40 @@
         <v>3</v>
       </c>
       <c r="E8" s="1">
+        <v>101</v>
+      </c>
+      <c r="F8" s="1">
+        <v>10</v>
+      </c>
+      <c r="G8" s="1">
         <v>1003</v>
       </c>
-      <c r="F8" s="1">
+      <c r="H8" s="1">
         <v>3</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="I8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4">
+        <v>5</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="4">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4">
-        <v>5</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+      <c r="N8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1335,34 +1377,40 @@
         <v>4</v>
       </c>
       <c r="E9" s="1">
+        <v>101</v>
+      </c>
+      <c r="F9" s="1">
+        <v>10</v>
+      </c>
+      <c r="G9" s="1">
         <v>1004</v>
       </c>
-      <c r="F9" s="1">
+      <c r="H9" s="1">
         <v>3</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="4">
+      <c r="I9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="4">
         <v>0</v>
       </c>
-      <c r="I9" s="4">
+      <c r="K9" s="4">
         <v>5</v>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="L9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M9" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+      <c r="M9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1370,31 +1418,35 @@
         <v>1</v>
       </c>
       <c r="E10" s="1">
+        <v>101</v>
+      </c>
+      <c r="F10" s="1">
+        <v>30</v>
+      </c>
+      <c r="G10" s="1">
         <v>1001</v>
       </c>
-      <c r="F10" s="1">
+      <c r="H10" s="1">
         <v>4</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" s="4">
+      <c r="I10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="4">
         <v>6</v>
       </c>
-      <c r="I10" s="4">
+      <c r="K10" s="4">
         <v>10</v>
       </c>
-      <c r="J10" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="L10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="XER10" s="1"/>
-      <c r="XES10" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="XET10" s="1"/>
       <c r="XEU10" s="1"/>
       <c r="XEV10" s="1"/>
@@ -1407,7 +1459,7 @@
       <c r="XFC10" s="1"/>
       <c r="XFD10" s="1"/>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1415,31 +1467,35 @@
         <v>2</v>
       </c>
       <c r="E11" s="1">
+        <v>101</v>
+      </c>
+      <c r="F11" s="1">
+        <v>30</v>
+      </c>
+      <c r="G11" s="1">
         <v>1002</v>
       </c>
-      <c r="F11" s="1">
+      <c r="H11" s="1">
         <v>4</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="4">
+      <c r="I11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="4">
         <v>6</v>
       </c>
-      <c r="I11" s="4">
+      <c r="K11" s="4">
         <v>10</v>
       </c>
-      <c r="J11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="L11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="XER11" s="1"/>
-      <c r="XES11" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="XET11" s="1"/>
       <c r="XEU11" s="1"/>
       <c r="XEV11" s="1"/>
@@ -1452,7 +1508,7 @@
       <c r="XFC11" s="1"/>
       <c r="XFD11" s="1"/>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1460,31 +1516,35 @@
         <v>3</v>
       </c>
       <c r="E12" s="1">
+        <v>101</v>
+      </c>
+      <c r="F12" s="1">
+        <v>30</v>
+      </c>
+      <c r="G12" s="1">
         <v>1003</v>
       </c>
-      <c r="F12" s="1">
+      <c r="H12" s="1">
         <v>4</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="I12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="4">
+        <v>6</v>
+      </c>
+      <c r="K12" s="4">
+        <v>10</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="4">
-        <v>6</v>
-      </c>
-      <c r="I12" s="4">
-        <v>10</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="XER12" s="1"/>
-      <c r="XES12" s="1"/>
+      <c r="N12" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="XET12" s="1"/>
       <c r="XEU12" s="1"/>
       <c r="XEV12" s="1"/>
@@ -1497,7 +1557,7 @@
       <c r="XFC12" s="1"/>
       <c r="XFD12" s="1"/>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1505,31 +1565,35 @@
         <v>4</v>
       </c>
       <c r="E13" s="1">
+        <v>101</v>
+      </c>
+      <c r="F13" s="1">
+        <v>30</v>
+      </c>
+      <c r="G13" s="1">
         <v>1004</v>
       </c>
-      <c r="F13" s="1">
+      <c r="H13" s="1">
         <v>4</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="4">
+      <c r="I13" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="4">
         <v>6</v>
       </c>
-      <c r="I13" s="4">
+      <c r="K13" s="4">
         <v>10</v>
       </c>
-      <c r="J13" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="L13" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="XER13" s="1"/>
-      <c r="XES13" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="XET13" s="1"/>
       <c r="XEU13" s="1"/>
       <c r="XEV13" s="1"/>
@@ -1542,19 +1606,19 @@
       <c r="XFC13" s="1"/>
       <c r="XFD13" s="1"/>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
       <c r="L14" s="1"/>
-      <c r="XER14" s="1"/>
-      <c r="XES14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
       <c r="XET14" s="1"/>
       <c r="XEU14" s="1"/>
       <c r="XEV14" s="1"/>
@@ -1567,19 +1631,19 @@
       <c r="XFC14" s="1"/>
       <c r="XFD14" s="1"/>
     </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
       <c r="I15" s="4"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
       <c r="L15" s="1"/>
-      <c r="XER15" s="1"/>
-      <c r="XES15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
       <c r="XET15" s="1"/>
       <c r="XEU15" s="1"/>
       <c r="XEV15" s="1"/>
@@ -1592,19 +1656,19 @@
       <c r="XFC15" s="1"/>
       <c r="XFD15" s="1"/>
     </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
       <c r="I16" s="4"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
       <c r="L16" s="1"/>
-      <c r="XER16" s="1"/>
-      <c r="XES16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
       <c r="XET16" s="1"/>
       <c r="XEU16" s="1"/>
       <c r="XEV16" s="1"/>
@@ -1617,19 +1681,19 @@
       <c r="XFC16" s="1"/>
       <c r="XFD16" s="1"/>
     </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
       <c r="L17" s="1"/>
-      <c r="XER17" s="1"/>
-      <c r="XES17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
       <c r="XET17" s="1"/>
       <c r="XEU17" s="1"/>
       <c r="XEV17" s="1"/>
@@ -1642,19 +1706,19 @@
       <c r="XFC17" s="1"/>
       <c r="XFD17" s="1"/>
     </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
       <c r="L18" s="1"/>
-      <c r="XER18" s="1"/>
-      <c r="XES18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
       <c r="XET18" s="1"/>
       <c r="XEU18" s="1"/>
       <c r="XEV18" s="1"/>
@@ -1667,19 +1731,19 @@
       <c r="XFC18" s="1"/>
       <c r="XFD18" s="1"/>
     </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
       <c r="I19" s="4"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
       <c r="L19" s="1"/>
-      <c r="XER19" s="1"/>
-      <c r="XES19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
       <c r="XET19" s="1"/>
       <c r="XEU19" s="1"/>
       <c r="XEV19" s="1"/>
@@ -1692,19 +1756,19 @@
       <c r="XFC19" s="1"/>
       <c r="XFD19" s="1"/>
     </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
       <c r="L20" s="1"/>
-      <c r="XER20" s="1"/>
-      <c r="XES20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
       <c r="XET20" s="1"/>
       <c r="XEU20" s="1"/>
       <c r="XEV20" s="1"/>
@@ -1717,19 +1781,19 @@
       <c r="XFC20" s="1"/>
       <c r="XFD20" s="1"/>
     </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
       <c r="L21" s="1"/>
-      <c r="XER21" s="1"/>
-      <c r="XES21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
       <c r="XET21" s="1"/>
       <c r="XEU21" s="1"/>
       <c r="XEV21" s="1"/>
@@ -1742,19 +1806,19 @@
       <c r="XFC21" s="1"/>
       <c r="XFD21" s="1"/>
     </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
       <c r="I22" s="4"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
       <c r="L22" s="1"/>
-      <c r="XER22" s="1"/>
-      <c r="XES22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
       <c r="XET22" s="1"/>
       <c r="XEU22" s="1"/>
       <c r="XEV22" s="1"/>
@@ -1767,19 +1831,19 @@
       <c r="XFC22" s="1"/>
       <c r="XFD22" s="1"/>
     </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
       <c r="I23" s="4"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
       <c r="L23" s="1"/>
-      <c r="XER23" s="1"/>
-      <c r="XES23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
       <c r="XET23" s="1"/>
       <c r="XEU23" s="1"/>
       <c r="XEV23" s="1"/>
@@ -1792,19 +1856,19 @@
       <c r="XFC23" s="1"/>
       <c r="XFD23" s="1"/>
     </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
       <c r="I24" s="4"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
       <c r="L24" s="1"/>
-      <c r="XER24" s="1"/>
-      <c r="XES24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
       <c r="XET24" s="1"/>
       <c r="XEU24" s="1"/>
       <c r="XEV24" s="1"/>
@@ -1817,19 +1881,19 @@
       <c r="XFC24" s="1"/>
       <c r="XFD24" s="1"/>
     </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
       <c r="I25" s="4"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
       <c r="L25" s="1"/>
-      <c r="XER25" s="1"/>
-      <c r="XES25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
       <c r="XET25" s="1"/>
       <c r="XEU25" s="1"/>
       <c r="XEV25" s="1"/>
@@ -1842,7 +1906,7 @@
       <c r="XFC25" s="1"/>
       <c r="XFD25" s="1"/>
     </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -1852,8 +1916,8 @@
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
-      <c r="XER26" s="1"/>
-      <c r="XES26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
       <c r="XET26" s="1"/>
       <c r="XEU26" s="1"/>
       <c r="XEV26" s="1"/>
@@ -1866,7 +1930,7 @@
       <c r="XFC26" s="1"/>
       <c r="XFD26" s="1"/>
     </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -1876,8 +1940,8 @@
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
-      <c r="XER27" s="1"/>
-      <c r="XES27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
       <c r="XET27" s="1"/>
       <c r="XEU27" s="1"/>
       <c r="XEV27" s="1"/>
@@ -1890,7 +1954,7 @@
       <c r="XFC27" s="1"/>
       <c r="XFD27" s="1"/>
     </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -1900,8 +1964,8 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
-      <c r="XER28" s="1"/>
-      <c r="XES28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
       <c r="XET28" s="1"/>
       <c r="XEU28" s="1"/>
       <c r="XEV28" s="1"/>
@@ -1914,7 +1978,7 @@
       <c r="XFC28" s="1"/>
       <c r="XFD28" s="1"/>
     </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -1924,8 +1988,8 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
-      <c r="XER29" s="1"/>
-      <c r="XES29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
       <c r="XET29" s="1"/>
       <c r="XEU29" s="1"/>
       <c r="XEV29" s="1"/>
@@ -1938,7 +2002,7 @@
       <c r="XFC29" s="1"/>
       <c r="XFD29" s="1"/>
     </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -1948,8 +2012,8 @@
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-      <c r="XER30" s="1"/>
-      <c r="XES30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
       <c r="XET30" s="1"/>
       <c r="XEU30" s="1"/>
       <c r="XEV30" s="1"/>
@@ -1962,7 +2026,7 @@
       <c r="XFC30" s="1"/>
       <c r="XFD30" s="1"/>
     </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -1972,8 +2036,8 @@
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
-      <c r="XER31" s="1"/>
-      <c r="XES31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
       <c r="XET31" s="1"/>
       <c r="XEU31" s="1"/>
       <c r="XEV31" s="1"/>
@@ -1986,7 +2050,7 @@
       <c r="XFC31" s="1"/>
       <c r="XFD31" s="1"/>
     </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -1996,8 +2060,8 @@
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
-      <c r="XER32" s="1"/>
-      <c r="XES32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
       <c r="XET32" s="1"/>
       <c r="XEU32" s="1"/>
       <c r="XEV32" s="1"/>
@@ -2010,7 +2074,7 @@
       <c r="XFC32" s="1"/>
       <c r="XFD32" s="1"/>
     </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -2020,8 +2084,8 @@
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
-      <c r="XER33" s="1"/>
-      <c r="XES33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
       <c r="XET33" s="1"/>
       <c r="XEU33" s="1"/>
       <c r="XEV33" s="1"/>
@@ -2034,7 +2098,7 @@
       <c r="XFC33" s="1"/>
       <c r="XFD33" s="1"/>
     </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -2044,8 +2108,8 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-      <c r="XER34" s="1"/>
-      <c r="XES34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
       <c r="XET34" s="1"/>
       <c r="XEU34" s="1"/>
       <c r="XEV34" s="1"/>
@@ -2058,7 +2122,7 @@
       <c r="XFC34" s="1"/>
       <c r="XFD34" s="1"/>
     </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -2068,8 +2132,8 @@
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
-      <c r="XER35" s="1"/>
-      <c r="XES35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
       <c r="XET35" s="1"/>
       <c r="XEU35" s="1"/>
       <c r="XEV35" s="1"/>
@@ -2082,7 +2146,7 @@
       <c r="XFC35" s="1"/>
       <c r="XFD35" s="1"/>
     </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -2092,8 +2156,8 @@
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-      <c r="XER36" s="1"/>
-      <c r="XES36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
       <c r="XET36" s="1"/>
       <c r="XEU36" s="1"/>
       <c r="XEV36" s="1"/>
@@ -2106,7 +2170,7 @@
       <c r="XFC36" s="1"/>
       <c r="XFD36" s="1"/>
     </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -2116,8 +2180,8 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="XER37" s="1"/>
-      <c r="XES37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
       <c r="XET37" s="1"/>
       <c r="XEU37" s="1"/>
       <c r="XEV37" s="1"/>
@@ -2130,7 +2194,7 @@
       <c r="XFC37" s="1"/>
       <c r="XFD37" s="1"/>
     </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -2140,8 +2204,8 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="XER38" s="1"/>
-      <c r="XES38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
       <c r="XET38" s="1"/>
       <c r="XEU38" s="1"/>
       <c r="XEV38" s="1"/>
@@ -2154,7 +2218,7 @@
       <c r="XFC38" s="1"/>
       <c r="XFD38" s="1"/>
     </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -2164,8 +2228,8 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
-      <c r="XER39" s="1"/>
-      <c r="XES39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
       <c r="XET39" s="1"/>
       <c r="XEU39" s="1"/>
       <c r="XEV39" s="1"/>
@@ -2178,7 +2242,7 @@
       <c r="XFC39" s="1"/>
       <c r="XFD39" s="1"/>
     </row>
-    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -2188,8 +2252,8 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
-      <c r="XER40" s="1"/>
-      <c r="XES40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
       <c r="XET40" s="1"/>
       <c r="XEU40" s="1"/>
       <c r="XEV40" s="1"/>
@@ -2202,7 +2266,7 @@
       <c r="XFC40" s="1"/>
       <c r="XFD40" s="1"/>
     </row>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -2212,8 +2276,8 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-      <c r="XER41" s="1"/>
-      <c r="XES41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
       <c r="XET41" s="1"/>
       <c r="XEU41" s="1"/>
       <c r="XEV41" s="1"/>
@@ -2226,7 +2290,7 @@
       <c r="XFC41" s="1"/>
       <c r="XFD41" s="1"/>
     </row>
-    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -2236,8 +2300,8 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
-      <c r="XER42" s="1"/>
-      <c r="XES42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
       <c r="XET42" s="1"/>
       <c r="XEU42" s="1"/>
       <c r="XEV42" s="1"/>
@@ -2250,7 +2314,7 @@
       <c r="XFC42" s="1"/>
       <c r="XFD42" s="1"/>
     </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -2260,8 +2324,8 @@
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
-      <c r="XER43" s="1"/>
-      <c r="XES43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
       <c r="XET43" s="1"/>
       <c r="XEU43" s="1"/>
       <c r="XEV43" s="1"/>
@@ -2274,7 +2338,7 @@
       <c r="XFC43" s="1"/>
       <c r="XFD43" s="1"/>
     </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -2284,8 +2348,8 @@
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
-      <c r="XER44" s="1"/>
-      <c r="XES44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
       <c r="XET44" s="1"/>
       <c r="XEU44" s="1"/>
       <c r="XEV44" s="1"/>
@@ -2298,7 +2362,7 @@
       <c r="XFC44" s="1"/>
       <c r="XFD44" s="1"/>
     </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -2308,8 +2372,8 @@
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
-      <c r="XER46" s="1"/>
-      <c r="XES46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
       <c r="XET46" s="1"/>
       <c r="XEU46" s="1"/>
       <c r="XEV46" s="1"/>
@@ -2322,7 +2386,7 @@
       <c r="XFC46" s="1"/>
       <c r="XFD46" s="1"/>
     </row>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -2332,8 +2396,8 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
-      <c r="XER47" s="1"/>
-      <c r="XES47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
       <c r="XET47" s="1"/>
       <c r="XEU47" s="1"/>
       <c r="XEV47" s="1"/>
@@ -2346,7 +2410,7 @@
       <c r="XFC47" s="1"/>
       <c r="XFD47" s="1"/>
     </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -2356,8 +2420,8 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
-      <c r="XER48" s="1"/>
-      <c r="XES48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
       <c r="XET48" s="1"/>
       <c r="XEU48" s="1"/>
       <c r="XEV48" s="1"/>
@@ -2370,7 +2434,7 @@
       <c r="XFC48" s="1"/>
       <c r="XFD48" s="1"/>
     </row>
-    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -2380,8 +2444,8 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
-      <c r="XER49" s="1"/>
-      <c r="XES49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
       <c r="XET49" s="1"/>
       <c r="XEU49" s="1"/>
       <c r="XEV49" s="1"/>
@@ -2394,7 +2458,7 @@
       <c r="XFC49" s="1"/>
       <c r="XFD49" s="1"/>
     </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -2404,8 +2468,8 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
-      <c r="XER50" s="1"/>
-      <c r="XES50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
       <c r="XET50" s="1"/>
       <c r="XEU50" s="1"/>
       <c r="XEV50" s="1"/>
@@ -2418,7 +2482,7 @@
       <c r="XFC50" s="1"/>
       <c r="XFD50" s="1"/>
     </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -2428,8 +2492,8 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
-      <c r="XER51" s="1"/>
-      <c r="XES51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
       <c r="XET51" s="1"/>
       <c r="XEU51" s="1"/>
       <c r="XEV51" s="1"/>
@@ -2442,7 +2506,7 @@
       <c r="XFC51" s="1"/>
       <c r="XFD51" s="1"/>
     </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -2452,8 +2516,8 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
-      <c r="XER52" s="1"/>
-      <c r="XES52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
       <c r="XET52" s="1"/>
       <c r="XEU52" s="1"/>
       <c r="XEV52" s="1"/>
@@ -2466,7 +2530,7 @@
       <c r="XFC52" s="1"/>
       <c r="XFD52" s="1"/>
     </row>
-    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -2476,8 +2540,8 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
-      <c r="XER53" s="1"/>
-      <c r="XES53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
       <c r="XET53" s="1"/>
       <c r="XEU53" s="1"/>
       <c r="XEV53" s="1"/>
@@ -2490,7 +2554,7 @@
       <c r="XFC53" s="1"/>
       <c r="XFD53" s="1"/>
     </row>
-    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -2500,8 +2564,8 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
-      <c r="XER54" s="1"/>
-      <c r="XES54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
       <c r="XET54" s="1"/>
       <c r="XEU54" s="1"/>
       <c r="XEV54" s="1"/>
@@ -2514,7 +2578,7 @@
       <c r="XFC54" s="1"/>
       <c r="XFD54" s="1"/>
     </row>
-    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -2524,8 +2588,8 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
-      <c r="XER55" s="1"/>
-      <c r="XES55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
       <c r="XET55" s="1"/>
       <c r="XEU55" s="1"/>
       <c r="XEV55" s="1"/>
@@ -2538,7 +2602,7 @@
       <c r="XFC55" s="1"/>
       <c r="XFD55" s="1"/>
     </row>
-    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -2548,8 +2612,8 @@
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
-      <c r="XER56" s="1"/>
-      <c r="XES56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
       <c r="XET56" s="1"/>
       <c r="XEU56" s="1"/>
       <c r="XEV56" s="1"/>
@@ -2562,7 +2626,7 @@
       <c r="XFC56" s="1"/>
       <c r="XFD56" s="1"/>
     </row>
-    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -2572,8 +2636,8 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
-      <c r="XER57" s="1"/>
-      <c r="XES57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
       <c r="XET57" s="1"/>
       <c r="XEU57" s="1"/>
       <c r="XEV57" s="1"/>
@@ -2586,7 +2650,7 @@
       <c r="XFC57" s="1"/>
       <c r="XFD57" s="1"/>
     </row>
-    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -2596,8 +2660,8 @@
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
-      <c r="XER58" s="1"/>
-      <c r="XES58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
       <c r="XET58" s="1"/>
       <c r="XEU58" s="1"/>
       <c r="XEV58" s="1"/>
@@ -2610,7 +2674,7 @@
       <c r="XFC58" s="1"/>
       <c r="XFD58" s="1"/>
     </row>
-    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -2620,8 +2684,8 @@
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
-      <c r="XER59" s="1"/>
-      <c r="XES59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
       <c r="XET59" s="1"/>
       <c r="XEU59" s="1"/>
       <c r="XEV59" s="1"/>
@@ -2634,7 +2698,7 @@
       <c r="XFC59" s="1"/>
       <c r="XFD59" s="1"/>
     </row>
-    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -2644,8 +2708,8 @@
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
-      <c r="XER60" s="1"/>
-      <c r="XES60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
       <c r="XET60" s="1"/>
       <c r="XEU60" s="1"/>
       <c r="XEV60" s="1"/>
@@ -2658,7 +2722,7 @@
       <c r="XFC60" s="1"/>
       <c r="XFD60" s="1"/>
     </row>
-    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -2668,8 +2732,8 @@
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
-      <c r="XER61" s="1"/>
-      <c r="XES61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
       <c r="XET61" s="1"/>
       <c r="XEU61" s="1"/>
       <c r="XEV61" s="1"/>
@@ -2682,7 +2746,7 @@
       <c r="XFC61" s="1"/>
       <c r="XFD61" s="1"/>
     </row>
-    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -2692,8 +2756,8 @@
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
-      <c r="XER62" s="1"/>
-      <c r="XES62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
       <c r="XET62" s="1"/>
       <c r="XEU62" s="1"/>
       <c r="XEV62" s="1"/>
@@ -2706,7 +2770,7 @@
       <c r="XFC62" s="1"/>
       <c r="XFD62" s="1"/>
     </row>
-    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -2716,8 +2780,8 @@
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
-      <c r="XER63" s="1"/>
-      <c r="XES63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
       <c r="XET63" s="1"/>
       <c r="XEU63" s="1"/>
       <c r="XEV63" s="1"/>
@@ -2730,7 +2794,7 @@
       <c r="XFC63" s="1"/>
       <c r="XFD63" s="1"/>
     </row>
-    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -2740,8 +2804,8 @@
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
-      <c r="XER64" s="1"/>
-      <c r="XES64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
       <c r="XET64" s="1"/>
       <c r="XEU64" s="1"/>
       <c r="XEV64" s="1"/>
@@ -2754,7 +2818,7 @@
       <c r="XFC64" s="1"/>
       <c r="XFD64" s="1"/>
     </row>
-    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -2764,8 +2828,8 @@
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
-      <c r="XER65" s="1"/>
-      <c r="XES65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
       <c r="XET65" s="1"/>
       <c r="XEU65" s="1"/>
       <c r="XEV65" s="1"/>
@@ -2778,7 +2842,7 @@
       <c r="XFC65" s="1"/>
       <c r="XFD65" s="1"/>
     </row>
-    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:11 16372:16384">
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:13 16374:16384">
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -2788,8 +2852,8 @@
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
-      <c r="XER66" s="1"/>
-      <c r="XES66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
       <c r="XET66" s="1"/>
       <c r="XEU66" s="1"/>
       <c r="XEV66" s="1"/>
@@ -2804,7 +2868,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5 F3:L5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:F5 C3:E5 G3:N5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipSpeicalConfig.xlsx
+++ b/Excel/EquipSpeicalConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="35">
   <si>
     <t>#</t>
   </si>
@@ -92,7 +92,7 @@
     <t>2,1002,21,2002</t>
   </si>
   <si>
-    <t>10,2,1,1</t>
+    <t>100,5,1,1</t>
   </si>
   <si>
     <t>暴击</t>
@@ -104,9 +104,6 @@
     <t>3,1003,23,2003</t>
   </si>
   <si>
-    <t>20,5,1,1</t>
-  </si>
-  <si>
     <t>致命</t>
   </si>
   <si>
@@ -125,10 +122,16 @@
     <t>1,1001,28,2001</t>
   </si>
   <si>
-    <t>200,10,1,1</t>
+    <t>2000,10,1,1</t>
   </si>
   <si>
     <t>减伤</t>
+  </si>
+  <si>
+    <t>500,10,5,5</t>
+  </si>
+  <si>
+    <t>10000,50,5,5</t>
   </si>
 </sst>
 </file>
@@ -1342,16 +1345,16 @@
         <v>24</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="O7" s="1">
         <v>5012</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:16 16375:16384">
@@ -1374,7 +1377,7 @@
         <v>3</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J8" s="5">
         <v>0</v>
@@ -1383,19 +1386,19 @@
         <v>5</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="O8" s="1">
         <v>5013</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:16 16375:16384">
@@ -1418,7 +1421,7 @@
         <v>3</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J9" s="5">
         <v>0</v>
@@ -1427,19 +1430,19 @@
         <v>5</v>
       </c>
       <c r="L9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="M9" s="6" t="s">
-        <v>32</v>
-      </c>
       <c r="N9" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O9" s="1">
         <v>5014</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="1:16 16375:16384">
@@ -1474,10 +1477,10 @@
         <v>20</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="O10" s="1">
         <v>5011</v>
@@ -1525,10 +1528,10 @@
         <v>24</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="O11" s="1">
         <v>5012</v>
@@ -1564,7 +1567,7 @@
         <v>4</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J12" s="5">
         <v>6</v>
@@ -1573,13 +1576,13 @@
         <v>10</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="O12" s="1">
         <v>5013</v>
@@ -1615,7 +1618,7 @@
         <v>4</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J13" s="5">
         <v>6</v>
@@ -1624,13 +1627,13 @@
         <v>10</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O13" s="1">
         <v>5014</v>
@@ -1648,7 +1651,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O3:O5 C3:N5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:O5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EquipSpeicalConfig.xlsx
+++ b/Excel/EquipSpeicalConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="46">
   <si>
     <t>#</t>
   </si>
@@ -89,30 +89,33 @@
     <t>灵盾</t>
   </si>
   <si>
-    <t>2,1002,21,2002</t>
+    <t>2,1002,22,2002</t>
+  </si>
+  <si>
+    <t>100,5,2,1</t>
+  </si>
+  <si>
+    <t>暴击</t>
+  </si>
+  <si>
+    <t>灵符</t>
+  </si>
+  <si>
+    <t>3,1003,24,2003</t>
+  </si>
+  <si>
+    <t>致命</t>
+  </si>
+  <si>
+    <t>灵玉</t>
+  </si>
+  <si>
+    <t>3,1003,27,2003</t>
   </si>
   <si>
     <t>100,5,1,1</t>
   </si>
   <si>
-    <t>暴击</t>
-  </si>
-  <si>
-    <t>灵符</t>
-  </si>
-  <si>
-    <t>3,1003,23,2003</t>
-  </si>
-  <si>
-    <t>致命</t>
-  </si>
-  <si>
-    <t>灵玉</t>
-  </si>
-  <si>
-    <t>3,1003,27,2003</t>
-  </si>
-  <si>
     <t>增伤</t>
   </si>
   <si>
@@ -128,10 +131,40 @@
     <t>减伤</t>
   </si>
   <si>
-    <t>500,10,5,5</t>
-  </si>
-  <si>
-    <t>10000,50,5,5</t>
+    <t>1000,35,15,7</t>
+  </si>
+  <si>
+    <t>500,10,5,2</t>
+  </si>
+  <si>
+    <t>1000,35,7,7</t>
+  </si>
+  <si>
+    <t>500,10,2,2</t>
+  </si>
+  <si>
+    <t>30000,70,7,7</t>
+  </si>
+  <si>
+    <t>20000,20,2,2</t>
+  </si>
+  <si>
+    <t>6000,90,45,20</t>
+  </si>
+  <si>
+    <t>3000,15,10,5</t>
+  </si>
+  <si>
+    <t>6000,90,20,20</t>
+  </si>
+  <si>
+    <t>3000,15,5,5</t>
+  </si>
+  <si>
+    <t>160000,180,20,20</t>
+  </si>
+  <si>
+    <t>50000,30,5,5</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1138,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD13"/>
+  <dimension ref="A1:XFD19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1115,14 +1148,14 @@
     <col min="10" max="10" width="12.4166666666667" style="1" customWidth="1"/>
     <col min="11" max="11" width="13.5416666666667" style="1" customWidth="1"/>
     <col min="12" max="12" width="27.5833333333333" style="2" customWidth="1"/>
-    <col min="13" max="13" width="20.25" style="2" customWidth="1"/>
-    <col min="14" max="14" width="18.8166666666667" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17.25" style="2" customWidth="1"/>
+    <col min="14" max="14" width="20.5" style="2" customWidth="1"/>
     <col min="15" max="15" width="13" style="3" customWidth="1"/>
-    <col min="16" max="16374" width="9" style="2"/>
-    <col min="16375" max="16384" width="9" style="1"/>
+    <col min="16" max="16375" width="9" style="2"/>
+    <col min="16376" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:16 16375:16384">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="L1" s="2"/>
@@ -1130,8 +1163,26 @@
       <c r="P1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="T1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:16 16375:16384">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="L2" s="2"/>
@@ -1139,8 +1190,26 @@
       <c r="P2" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="T2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:16 16375:16384">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="4" t="s">
@@ -1183,7 +1252,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:16 16375:16384">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="4" t="s">
@@ -1226,7 +1295,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:16 16375:16384">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="4" t="s">
@@ -1269,7 +1338,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:16 16375:16384">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1286,7 +1355,7 @@
         <v>1001</v>
       </c>
       <c r="H6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>19</v>
@@ -1295,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>20</v>
@@ -1312,8 +1381,26 @@
       <c r="P6" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="T6" s="1">
+        <v>2000</v>
+      </c>
+      <c r="U6" s="1">
+        <v>100</v>
+      </c>
+      <c r="V6" s="1">
+        <v>10</v>
+      </c>
+      <c r="W6" s="1">
+        <v>5</v>
+      </c>
+      <c r="X6" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:16 16375:16384">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1330,7 +1417,7 @@
         <v>1002</v>
       </c>
       <c r="H7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>23</v>
@@ -1339,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>24</v>
@@ -1357,7 +1444,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:16 16375:16384">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1374,7 +1461,7 @@
         <v>1003</v>
       </c>
       <c r="H8" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>26</v>
@@ -1383,25 +1470,25 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>27</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="O8" s="1">
         <v>5013</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:16 16375:16384">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1418,90 +1505,68 @@
         <v>1004</v>
       </c>
       <c r="H9" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J9" s="5">
         <v>0</v>
       </c>
       <c r="K9" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O9" s="1">
         <v>5014</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:16 16375:16384">
-      <c r="C10" s="1">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="T10" s="2">
+        <f t="shared" ref="T10:Y10" si="0">T6*5</f>
+        <v>10000</v>
+      </c>
+      <c r="U10" s="2">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="V10" s="2">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="W10" s="2">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="X10" s="2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="Y10" s="2">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="D10" s="1">
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+      <c r="D11" s="1">
         <v>1</v>
-      </c>
-      <c r="E10" s="1">
-        <v>101</v>
-      </c>
-      <c r="F10" s="1">
-        <v>30</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1001</v>
-      </c>
-      <c r="H10" s="1">
-        <v>4</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="5">
-        <v>6</v>
-      </c>
-      <c r="K10" s="5">
-        <v>10</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O10" s="1">
-        <v>5011</v>
-      </c>
-      <c r="XEU10" s="1"/>
-      <c r="XEV10" s="1"/>
-      <c r="XEW10" s="1"/>
-      <c r="XEX10" s="1"/>
-      <c r="XEY10" s="1"/>
-      <c r="XEZ10" s="1"/>
-      <c r="XFA10" s="1"/>
-      <c r="XFB10" s="1"/>
-      <c r="XFC10" s="1"/>
-      <c r="XFD10" s="1"/>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:16 16375:16384">
-      <c r="C11" s="1">
-        <v>6</v>
-      </c>
-      <c r="D11" s="1">
-        <v>2</v>
       </c>
       <c r="E11" s="1">
         <v>101</v>
@@ -1510,33 +1575,50 @@
         <v>30</v>
       </c>
       <c r="G11" s="1">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="H11" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J11" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K11" s="5">
+        <v>9</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O11" s="1">
+        <v>5011</v>
+      </c>
+      <c r="T11" s="2">
+        <v>20000</v>
+      </c>
+      <c r="U11" s="2">
+        <v>500</v>
+      </c>
+      <c r="V11" s="2">
+        <v>20</v>
+      </c>
+      <c r="W11" s="2">
         <v>10</v>
       </c>
-      <c r="L11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="O11" s="1">
-        <v>5012</v>
-      </c>
-      <c r="XEU11" s="1"/>
+      <c r="X11" s="2">
+        <v>5</v>
+      </c>
+      <c r="Y11" s="2">
+        <v>2</v>
+      </c>
       <c r="XEV11" s="1"/>
       <c r="XEW11" s="1"/>
       <c r="XEX11" s="1"/>
@@ -1547,12 +1629,12 @@
       <c r="XFC11" s="1"/>
       <c r="XFD11" s="1"/>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:16 16375:16384">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:25 16376:16384">
       <c r="C12" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D12" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="1">
         <v>101</v>
@@ -1561,33 +1643,56 @@
         <v>30</v>
       </c>
       <c r="G12" s="1">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H12" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J12" s="5">
         <v>6</v>
       </c>
       <c r="K12" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O12" s="1">
-        <v>5013</v>
-      </c>
-      <c r="XEU12" s="1"/>
+        <v>5012</v>
+      </c>
+      <c r="T12" s="2">
+        <f t="shared" ref="T12:Y12" si="1">T10+T11</f>
+        <v>30000</v>
+      </c>
+      <c r="U12" s="2">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="V12" s="2">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="W12" s="2">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="X12" s="2">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="Y12" s="2">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
       <c r="XEV12" s="1"/>
       <c r="XEW12" s="1"/>
       <c r="XEX12" s="1"/>
@@ -1598,12 +1703,12 @@
       <c r="XFC12" s="1"/>
       <c r="XFD12" s="1"/>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:16 16375:16384">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:25 16376:16384">
       <c r="C13" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D13" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" s="1">
         <v>101</v>
@@ -1612,33 +1717,32 @@
         <v>30</v>
       </c>
       <c r="G13" s="1">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H13" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J13" s="5">
         <v>6</v>
       </c>
       <c r="K13" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O13" s="1">
-        <v>5014</v>
-      </c>
-      <c r="XEU13" s="1"/>
+        <v>5013</v>
+      </c>
       <c r="XEV13" s="1"/>
       <c r="XEW13" s="1"/>
       <c r="XEX13" s="1"/>
@@ -1648,6 +1752,310 @@
       <c r="XFB13" s="1"/>
       <c r="XFC13" s="1"/>
       <c r="XFD13" s="1"/>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+      <c r="C14" s="1">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1">
+        <v>101</v>
+      </c>
+      <c r="F14" s="1">
+        <v>30</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1004</v>
+      </c>
+      <c r="H14" s="1">
+        <v>3</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" s="5">
+        <v>6</v>
+      </c>
+      <c r="K14" s="5">
+        <v>9</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="O14" s="1">
+        <v>5014</v>
+      </c>
+      <c r="XEV14" s="1"/>
+      <c r="XEW14" s="1"/>
+      <c r="XEX14" s="1"/>
+      <c r="XEY14" s="1"/>
+      <c r="XEZ14" s="1"/>
+      <c r="XFA14" s="1"/>
+      <c r="XFB14" s="1"/>
+      <c r="XFC14" s="1"/>
+      <c r="XFD14" s="1"/>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="T15" s="2">
+        <f t="shared" ref="T15:Y15" si="2">T12+T11*4</f>
+        <v>110000</v>
+      </c>
+      <c r="U15" s="2">
+        <f t="shared" si="2"/>
+        <v>3000</v>
+      </c>
+      <c r="V15" s="2">
+        <f t="shared" si="2"/>
+        <v>150</v>
+      </c>
+      <c r="W15" s="2">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+      <c r="X15" s="2">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="Y15" s="2">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="XEV15" s="1"/>
+      <c r="XEW15" s="1"/>
+      <c r="XEX15" s="1"/>
+      <c r="XEY15" s="1"/>
+      <c r="XEZ15" s="1"/>
+      <c r="XFA15" s="1"/>
+      <c r="XFB15" s="1"/>
+      <c r="XFC15" s="1"/>
+      <c r="XFD15" s="1"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:25 16376:16384">
+      <c r="C16" s="1">
+        <v>9</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>101</v>
+      </c>
+      <c r="F16" s="1">
+        <v>30</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1001</v>
+      </c>
+      <c r="H16" s="1">
+        <v>4</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" s="5">
+        <v>10</v>
+      </c>
+      <c r="K16" s="5">
+        <v>14</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="O16" s="1">
+        <v>5011</v>
+      </c>
+      <c r="T16" s="2">
+        <v>50000</v>
+      </c>
+      <c r="U16" s="2">
+        <v>3000</v>
+      </c>
+      <c r="V16" s="2">
+        <v>30</v>
+      </c>
+      <c r="W16" s="2">
+        <v>15</v>
+      </c>
+      <c r="X16" s="2">
+        <v>10</v>
+      </c>
+      <c r="Y16" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:25">
+      <c r="C17" s="1">
+        <v>10</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>101</v>
+      </c>
+      <c r="F17" s="1">
+        <v>30</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1002</v>
+      </c>
+      <c r="H17" s="1">
+        <v>4</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="5">
+        <v>10</v>
+      </c>
+      <c r="K17" s="5">
+        <v>14</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="O17" s="1">
+        <v>5012</v>
+      </c>
+      <c r="T17" s="2">
+        <f t="shared" ref="T17:Y17" si="3">T15+T16</f>
+        <v>160000</v>
+      </c>
+      <c r="U17" s="2">
+        <f t="shared" si="3"/>
+        <v>6000</v>
+      </c>
+      <c r="V17" s="2">
+        <f t="shared" si="3"/>
+        <v>180</v>
+      </c>
+      <c r="W17" s="2">
+        <f t="shared" si="3"/>
+        <v>90</v>
+      </c>
+      <c r="X17" s="2">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="Y17" s="2">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:25">
+      <c r="C18" s="1">
+        <v>11</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1">
+        <v>101</v>
+      </c>
+      <c r="F18" s="1">
+        <v>30</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1003</v>
+      </c>
+      <c r="H18" s="1">
+        <v>4</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" s="5">
+        <v>10</v>
+      </c>
+      <c r="K18" s="5">
+        <v>14</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O18" s="1">
+        <v>5013</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:25">
+      <c r="C19" s="1">
+        <v>12</v>
+      </c>
+      <c r="D19" s="1">
+        <v>4</v>
+      </c>
+      <c r="E19" s="1">
+        <v>101</v>
+      </c>
+      <c r="F19" s="1">
+        <v>30</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1004</v>
+      </c>
+      <c r="H19" s="1">
+        <v>4</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19" s="5">
+        <v>10</v>
+      </c>
+      <c r="K19" s="5">
+        <v>14</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="O19" s="1">
+        <v>5014</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/EquipSpeicalConfig.xlsx
+++ b/Excel/EquipSpeicalConfig.xlsx
@@ -1652,7 +1652,7 @@
         <v>23</v>
       </c>
       <c r="J12" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K12" s="5">
         <v>9</v>
@@ -1726,7 +1726,7 @@
         <v>26</v>
       </c>
       <c r="J13" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K13" s="5">
         <v>9</v>
@@ -1776,7 +1776,7 @@
         <v>30</v>
       </c>
       <c r="J14" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K14" s="5">
         <v>9</v>

--- a/Excel/EquipSpeicalConfig.xlsx
+++ b/Excel/EquipSpeicalConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="41">
   <si>
     <t>#</t>
   </si>
@@ -110,10 +110,10 @@
     <t>灵玉</t>
   </si>
   <si>
-    <t>3,1003,27,2003</t>
-  </si>
-  <si>
-    <t>100,5,1,1</t>
+    <t>1,1001,27,2001</t>
+  </si>
+  <si>
+    <t>2000,10,1,1</t>
   </si>
   <si>
     <t>增伤</t>
@@ -125,9 +125,6 @@
     <t>1,1001,28,2001</t>
   </si>
   <si>
-    <t>2000,10,1,1</t>
-  </si>
-  <si>
     <t>减伤</t>
   </si>
   <si>
@@ -137,12 +134,6 @@
     <t>500,10,5,2</t>
   </si>
   <si>
-    <t>1000,35,7,7</t>
-  </si>
-  <si>
-    <t>500,10,2,2</t>
-  </si>
-  <si>
     <t>30000,70,7,7</t>
   </si>
   <si>
@@ -153,12 +144,6 @@
   </si>
   <si>
     <t>3000,15,10,5</t>
-  </si>
-  <si>
-    <t>6000,90,20,20</t>
-  </si>
-  <si>
-    <t>3000,15,5,5</t>
   </si>
   <si>
     <t>160000,180,20,20</t>
@@ -1520,16 +1505,16 @@
         <v>31</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="O9" s="1">
         <v>5014</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
@@ -1593,10 +1578,10 @@
         <v>20</v>
       </c>
       <c r="M11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N11" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>35</v>
       </c>
       <c r="O11" s="1">
         <v>5011</v>
@@ -1661,10 +1646,10 @@
         <v>24</v>
       </c>
       <c r="M12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N12" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>35</v>
       </c>
       <c r="O12" s="1">
         <v>5012</v>
@@ -1735,10 +1720,10 @@
         <v>27</v>
       </c>
       <c r="M13" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N13" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="O13" s="1">
         <v>5013</v>
@@ -1785,10 +1770,10 @@
         <v>31</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="O14" s="1">
         <v>5014</v>
@@ -1883,10 +1868,10 @@
         <v>20</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="O16" s="1">
         <v>5011</v>
@@ -1942,10 +1927,10 @@
         <v>24</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="O17" s="1">
         <v>5012</v>
@@ -2007,10 +1992,10 @@
         <v>27</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="O18" s="1">
         <v>5013</v>
@@ -2048,10 +2033,10 @@
         <v>31</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="O19" s="1">
         <v>5014</v>

--- a/Excel/EquipSpeicalConfig.xlsx
+++ b/Excel/EquipSpeicalConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="59">
   <si>
     <t>#</t>
   </si>
@@ -86,70 +86,124 @@
     <t>double[]</t>
   </si>
   <si>
+    <t>生命</t>
+  </si>
+  <si>
+    <t>防御、攻击</t>
+  </si>
+  <si>
+    <t>三维加成</t>
+  </si>
+  <si>
+    <t>爆伤、致命</t>
+  </si>
+  <si>
+    <t>增伤、减伤</t>
+  </si>
+  <si>
+    <t>增幅</t>
+  </si>
+  <si>
     <t>灵盾</t>
   </si>
   <si>
+    <t>2,1002,22</t>
+  </si>
+  <si>
+    <t>100,5,2</t>
+  </si>
+  <si>
+    <t>暴击</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>灵符</t>
+  </si>
+  <si>
+    <t>3,1003,24</t>
+  </si>
+  <si>
+    <t>致命</t>
+  </si>
+  <si>
+    <t>5-9</t>
+  </si>
+  <si>
+    <t>灵玉</t>
+  </si>
+  <si>
+    <t>1,1001,27</t>
+  </si>
+  <si>
+    <t>2000,10,1</t>
+  </si>
+  <si>
+    <t>2000,5,1</t>
+  </si>
+  <si>
+    <t>增伤</t>
+  </si>
+  <si>
+    <t>10-14</t>
+  </si>
+  <si>
+    <t>灵珠</t>
+  </si>
+  <si>
+    <t>1,1001,28</t>
+  </si>
+  <si>
+    <t>减伤</t>
+  </si>
+  <si>
+    <t>15-19</t>
+  </si>
+  <si>
+    <t>20-24</t>
+  </si>
+  <si>
     <t>2,1002,22,2002</t>
   </si>
   <si>
-    <t>100,5,2,1</t>
-  </si>
-  <si>
-    <t>暴击</t>
-  </si>
-  <si>
-    <t>灵符</t>
+    <t>1000,35,14,1</t>
+  </si>
+  <si>
+    <t>500,10,4,1</t>
+  </si>
+  <si>
+    <t>25-29</t>
   </si>
   <si>
     <t>3,1003,24,2003</t>
   </si>
   <si>
-    <t>致命</t>
-  </si>
-  <si>
-    <t>灵玉</t>
+    <t>30-24</t>
   </si>
   <si>
     <t>1,1001,27,2001</t>
   </si>
   <si>
-    <t>2000,10,1,1</t>
-  </si>
-  <si>
-    <t>增伤</t>
-  </si>
-  <si>
-    <t>灵珠</t>
+    <t>20000,35,7,1</t>
+  </si>
+  <si>
+    <t>10000,10,2,1</t>
   </si>
   <si>
     <t>1,1001,28,2001</t>
   </si>
   <si>
-    <t>减伤</t>
-  </si>
-  <si>
-    <t>1000,35,15,7</t>
-  </si>
-  <si>
-    <t>500,10,5,2</t>
-  </si>
-  <si>
-    <t>30000,70,7,7</t>
-  </si>
-  <si>
-    <t>20000,20,2,2</t>
-  </si>
-  <si>
-    <t>6000,90,45,20</t>
-  </si>
-  <si>
-    <t>3000,15,10,5</t>
-  </si>
-  <si>
-    <t>160000,180,20,20</t>
-  </si>
-  <si>
-    <t>50000,30,5,5</t>
+    <t>6000,100,40,8</t>
+  </si>
+  <si>
+    <t>3000,15,6,2</t>
+  </si>
+  <si>
+    <t>120000,100,20,8</t>
+  </si>
+  <si>
+    <t>60000,15,3,2</t>
   </si>
 </sst>
 </file>
@@ -794,7 +848,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -803,7 +857,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1123,24 +1179,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD19"/>
+  <dimension ref="A1:XFB19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="8" width="9.875" style="1" customWidth="1"/>
     <col min="9" max="9" width="15.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.4166666666667" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5416666666667" style="1" customWidth="1"/>
-    <col min="12" max="12" width="27.5833333333333" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.08333333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.0833333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="20" style="2" customWidth="1"/>
     <col min="13" max="13" width="17.25" style="2" customWidth="1"/>
     <col min="14" max="14" width="20.5" style="2" customWidth="1"/>
     <col min="15" max="15" width="13" style="3" customWidth="1"/>
-    <col min="16" max="16375" width="9" style="2"/>
-    <col min="16376" max="16384" width="9" style="1"/>
+    <col min="16" max="18" width="9" style="2"/>
+    <col min="19" max="19" width="7" style="2" customWidth="1"/>
+    <col min="20" max="20" width="11.0833333333333" style="2" customWidth="1"/>
+    <col min="21" max="22" width="9" style="2"/>
+    <col min="23" max="23" width="8.58333333333333" style="2" customWidth="1"/>
+    <col min="24" max="24" width="10.1666666666667" style="2" customWidth="1"/>
+    <col min="25" max="16374" width="9" style="2"/>
+    <col min="16375" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:25 16375:16382">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="L1" s="2"/>
@@ -1148,6 +1210,9 @@
       <c r="P1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="S1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="T1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1163,11 +1228,8 @@
       <c r="X1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:25 16375:16382">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="L2" s="2"/>
@@ -1175,6 +1237,9 @@
       <c r="P2" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="S2" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="T2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1190,11 +1255,8 @@
       <c r="X2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="Y2" s="1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:25 16375:16382">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="4" t="s">
@@ -1237,7 +1299,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:25 16375:16382">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="4" t="s">
@@ -1280,7 +1342,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:25 16375:16382">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="4" t="s">
@@ -1322,8 +1384,26 @@
       <c r="O5" s="4" t="s">
         <v>15</v>
       </c>
+      <c r="T5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:25 16375:16382">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1343,7 +1423,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J6" s="5">
         <v>0</v>
@@ -1351,20 +1431,23 @@
       <c r="K6" s="5">
         <v>4</v>
       </c>
-      <c r="L6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>21</v>
+      <c r="L6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="O6" s="1">
         <v>5011</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="T6" s="1">
         <v>2000</v>
@@ -1373,19 +1456,19 @@
         <v>100</v>
       </c>
       <c r="V6" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W6" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:25 16375:16382">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1405,7 +1488,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J7" s="5">
         <v>0</v>
@@ -1413,23 +1496,44 @@
       <c r="K7" s="5">
         <v>4</v>
       </c>
-      <c r="L7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>21</v>
+      <c r="L7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="O7" s="1">
         <v>5012</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
+      </c>
+      <c r="S7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="T7" s="1">
+        <v>10000</v>
+      </c>
+      <c r="U7" s="1">
+        <v>500</v>
+      </c>
+      <c r="V7" s="1">
+        <v>10</v>
+      </c>
+      <c r="W7" s="1">
+        <v>4</v>
+      </c>
+      <c r="X7" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>1</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:25 16375:16382">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1449,7 +1553,7 @@
         <v>2</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J8" s="5">
         <v>0</v>
@@ -1457,23 +1561,44 @@
       <c r="K8" s="5">
         <v>4</v>
       </c>
-      <c r="L8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>28</v>
+      <c r="L8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="O8" s="1">
         <v>5013</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="S8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="T8" s="1">
+        <v>50000</v>
+      </c>
+      <c r="U8" s="1">
+        <v>3000</v>
+      </c>
+      <c r="V8" s="1">
+        <v>15</v>
+      </c>
+      <c r="W8" s="1">
+        <v>6</v>
+      </c>
+      <c r="X8" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>2</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:25 16375:16382">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1493,7 +1618,7 @@
         <v>2</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J9" s="5">
         <v>0</v>
@@ -1501,52 +1626,39 @@
       <c r="K9" s="5">
         <v>4</v>
       </c>
-      <c r="L9" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>28</v>
+      <c r="L9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="O9" s="1">
         <v>5014</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>32</v>
+        <v>42</v>
+      </c>
+      <c r="S9" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:25 16375:16382">
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
-      <c r="T10" s="2">
-        <f t="shared" ref="T10:Y10" si="0">T6*5</f>
-        <v>10000</v>
-      </c>
-      <c r="U10" s="2">
-        <f t="shared" si="0"/>
-        <v>500</v>
-      </c>
-      <c r="V10" s="2">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="W10" s="2">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="X10" s="2">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="Y10" s="2">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
+      <c r="S10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:25 16375:16382">
       <c r="C11" s="1">
         <v>5</v>
       </c>
@@ -1557,7 +1669,7 @@
         <v>101</v>
       </c>
       <c r="F11" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G11" s="1">
         <v>1001</v>
@@ -1566,7 +1678,7 @@
         <v>3</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J11" s="5">
         <v>5</v>
@@ -1574,36 +1686,27 @@
       <c r="K11" s="5">
         <v>9</v>
       </c>
-      <c r="L11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>34</v>
+      <c r="L11" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="O11" s="1">
         <v>5011</v>
       </c>
-      <c r="T11" s="2">
-        <v>20000</v>
-      </c>
-      <c r="U11" s="2">
-        <v>500</v>
-      </c>
-      <c r="V11" s="2">
-        <v>20</v>
-      </c>
-      <c r="W11" s="2">
-        <v>10</v>
-      </c>
-      <c r="X11" s="2">
-        <v>5</v>
-      </c>
-      <c r="Y11" s="2">
-        <v>2</v>
-      </c>
+      <c r="S11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="XEU11" s="1"/>
       <c r="XEV11" s="1"/>
       <c r="XEW11" s="1"/>
       <c r="XEX11" s="1"/>
@@ -1611,10 +1714,8 @@
       <c r="XEZ11" s="1"/>
       <c r="XFA11" s="1"/>
       <c r="XFB11" s="1"/>
-      <c r="XFC11" s="1"/>
-      <c r="XFD11" s="1"/>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:25 16375:16382">
       <c r="C12" s="1">
         <v>6</v>
       </c>
@@ -1625,7 +1726,7 @@
         <v>101</v>
       </c>
       <c r="F12" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G12" s="1">
         <v>1002</v>
@@ -1634,7 +1735,7 @@
         <v>3</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J12" s="5">
         <v>5</v>
@@ -1642,42 +1743,27 @@
       <c r="K12" s="5">
         <v>9</v>
       </c>
-      <c r="L12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>34</v>
+      <c r="L12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="O12" s="1">
         <v>5012</v>
       </c>
-      <c r="T12" s="2">
-        <f t="shared" ref="T12:Y12" si="1">T10+T11</f>
-        <v>30000</v>
-      </c>
-      <c r="U12" s="2">
-        <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="V12" s="2">
-        <f t="shared" si="1"/>
-        <v>70</v>
-      </c>
-      <c r="W12" s="2">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="X12" s="2">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="Y12" s="2">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
+      <c r="S12" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="XEU12" s="1"/>
       <c r="XEV12" s="1"/>
       <c r="XEW12" s="1"/>
       <c r="XEX12" s="1"/>
@@ -1685,10 +1771,8 @@
       <c r="XEZ12" s="1"/>
       <c r="XFA12" s="1"/>
       <c r="XFB12" s="1"/>
-      <c r="XFC12" s="1"/>
-      <c r="XFD12" s="1"/>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:25 16375:16382">
       <c r="C13" s="1">
         <v>7</v>
       </c>
@@ -1699,7 +1783,7 @@
         <v>101</v>
       </c>
       <c r="F13" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G13" s="1">
         <v>1003</v>
@@ -1708,7 +1792,7 @@
         <v>3</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J13" s="5">
         <v>5</v>
@@ -1716,18 +1800,19 @@
       <c r="K13" s="5">
         <v>9</v>
       </c>
-      <c r="L13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>36</v>
+      <c r="L13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="O13" s="1">
         <v>5013</v>
       </c>
+      <c r="XEU13" s="1"/>
       <c r="XEV13" s="1"/>
       <c r="XEW13" s="1"/>
       <c r="XEX13" s="1"/>
@@ -1735,10 +1820,8 @@
       <c r="XEZ13" s="1"/>
       <c r="XFA13" s="1"/>
       <c r="XFB13" s="1"/>
-      <c r="XFC13" s="1"/>
-      <c r="XFD13" s="1"/>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:25 16375:16382">
       <c r="C14" s="1">
         <v>8</v>
       </c>
@@ -1749,7 +1832,7 @@
         <v>101</v>
       </c>
       <c r="F14" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G14" s="1">
         <v>1004</v>
@@ -1758,7 +1841,7 @@
         <v>3</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J14" s="5">
         <v>5</v>
@@ -1766,18 +1849,37 @@
       <c r="K14" s="5">
         <v>9</v>
       </c>
-      <c r="L14" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>36</v>
+      <c r="L14" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="O14" s="1">
         <v>5014</v>
       </c>
+      <c r="T14" s="2">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2">
+        <v>0</v>
+      </c>
+      <c r="W14" s="2">
+        <v>0</v>
+      </c>
+      <c r="X14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="2">
+        <v>0</v>
+      </c>
+      <c r="XEU14" s="1"/>
       <c r="XEV14" s="1"/>
       <c r="XEW14" s="1"/>
       <c r="XEX14" s="1"/>
@@ -1785,10 +1887,8 @@
       <c r="XEZ14" s="1"/>
       <c r="XFA14" s="1"/>
       <c r="XFB14" s="1"/>
-      <c r="XFC14" s="1"/>
-      <c r="XFD14" s="1"/>
     </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:25 16376:16384">
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:25 16375:16382">
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -1803,29 +1903,30 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="T15" s="2">
-        <f t="shared" ref="T15:Y15" si="2">T12+T11*4</f>
-        <v>110000</v>
+        <f>T14+T6*5+T7</f>
+        <v>20000</v>
       </c>
       <c r="U15" s="2">
-        <f t="shared" si="2"/>
-        <v>3000</v>
+        <f>U14+U6*5+U7</f>
+        <v>1000</v>
       </c>
       <c r="V15" s="2">
-        <f t="shared" si="2"/>
-        <v>150</v>
+        <f>V14+V6*5+V7</f>
+        <v>35</v>
       </c>
       <c r="W15" s="2">
-        <f t="shared" si="2"/>
-        <v>75</v>
+        <f>W14+W6*5+W7</f>
+        <v>14</v>
       </c>
       <c r="X15" s="2">
-        <f t="shared" si="2"/>
-        <v>35</v>
+        <f>X14+X6*5+X7</f>
+        <v>7</v>
       </c>
       <c r="Y15" s="2">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
+        <f>Y14+Y6*5+Y7</f>
+        <v>1</v>
+      </c>
+      <c r="XEU15" s="1"/>
       <c r="XEV15" s="1"/>
       <c r="XEW15" s="1"/>
       <c r="XEX15" s="1"/>
@@ -1833,10 +1934,8 @@
       <c r="XEZ15" s="1"/>
       <c r="XFA15" s="1"/>
       <c r="XFB15" s="1"/>
-      <c r="XFC15" s="1"/>
-      <c r="XFD15" s="1"/>
     </row>
-    <row r="16" customHeight="1" spans="1:25 16376:16384">
+    <row r="16" customHeight="1" spans="1:25 16375:16382">
       <c r="C16" s="1">
         <v>9</v>
       </c>
@@ -1856,7 +1955,7 @@
         <v>4</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J16" s="5">
         <v>10</v>
@@ -1864,38 +1963,44 @@
       <c r="K16" s="5">
         <v>14</v>
       </c>
-      <c r="L16" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="M16" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>38</v>
+      <c r="L16" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="O16" s="1">
         <v>5011</v>
       </c>
       <c r="T16" s="2">
-        <v>50000</v>
+        <f>T15+T7*5+T8</f>
+        <v>120000</v>
       </c>
       <c r="U16" s="2">
-        <v>3000</v>
+        <f>U15+U7*5+U8</f>
+        <v>6500</v>
       </c>
       <c r="V16" s="2">
-        <v>30</v>
+        <f>V15+V7*5+V8</f>
+        <v>100</v>
       </c>
       <c r="W16" s="2">
-        <v>15</v>
+        <f>W15+W7*5+W8</f>
+        <v>40</v>
       </c>
       <c r="X16" s="2">
-        <v>10</v>
+        <f>X15+X7*5+X8</f>
+        <v>20</v>
       </c>
       <c r="Y16" s="2">
-        <v>5</v>
+        <f>Y15+Y7*5+Y8</f>
+        <v>8</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="3:25">
+    <row r="17" customHeight="1" spans="3:15">
       <c r="C17" s="1">
         <v>10</v>
       </c>
@@ -1915,7 +2020,7 @@
         <v>4</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J17" s="5">
         <v>10</v>
@@ -1923,44 +2028,20 @@
       <c r="K17" s="5">
         <v>14</v>
       </c>
-      <c r="L17" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M17" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="N17" s="6" t="s">
-        <v>38</v>
+      <c r="L17" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="O17" s="1">
         <v>5012</v>
       </c>
-      <c r="T17" s="2">
-        <f t="shared" ref="T17:Y17" si="3">T15+T16</f>
-        <v>160000</v>
-      </c>
-      <c r="U17" s="2">
-        <f t="shared" si="3"/>
-        <v>6000</v>
-      </c>
-      <c r="V17" s="2">
-        <f t="shared" si="3"/>
-        <v>180</v>
-      </c>
-      <c r="W17" s="2">
-        <f t="shared" si="3"/>
-        <v>90</v>
-      </c>
-      <c r="X17" s="2">
-        <f t="shared" si="3"/>
-        <v>45</v>
-      </c>
-      <c r="Y17" s="2">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
     </row>
-    <row r="18" customHeight="1" spans="3:25">
+    <row r="18" customHeight="1" spans="3:15">
       <c r="C18" s="1">
         <v>11</v>
       </c>
@@ -1980,7 +2061,7 @@
         <v>4</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J18" s="5">
         <v>10</v>
@@ -1988,20 +2069,20 @@
       <c r="K18" s="5">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>40</v>
+      <c r="L18" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="O18" s="1">
         <v>5013</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="3:25">
+    <row r="19" customHeight="1" spans="3:15">
       <c r="C19" s="1">
         <v>12</v>
       </c>
@@ -2021,7 +2102,7 @@
         <v>4</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J19" s="5">
         <v>10</v>
@@ -2029,14 +2110,14 @@
       <c r="K19" s="5">
         <v>14</v>
       </c>
-      <c r="L19" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M19" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="N19" s="6" t="s">
-        <v>40</v>
+      <c r="L19" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="O19" s="1">
         <v>5014</v>

--- a/Excel/EquipSpeicalConfig.xlsx
+++ b/Excel/EquipSpeicalConfig.xlsx
@@ -197,13 +197,13 @@
     <t>6000,100,40,8</t>
   </si>
   <si>
-    <t>3000,15,6,2</t>
+    <t>2500,15,6,2</t>
   </si>
   <si>
     <t>120000,100,20,8</t>
   </si>
   <si>
-    <t>60000,15,3,2</t>
+    <t>50000,15,3,2</t>
   </si>
 </sst>
 </file>
@@ -1583,7 +1583,7 @@
         <v>50000</v>
       </c>
       <c r="U8" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="V8" s="1">
         <v>15</v>
@@ -1643,6 +1643,24 @@
       </c>
       <c r="S9" s="7" t="s">
         <v>43</v>
+      </c>
+      <c r="T9" s="1">
+        <v>200000</v>
+      </c>
+      <c r="U9" s="1">
+        <v>10000</v>
+      </c>
+      <c r="V9" s="1">
+        <v>20</v>
+      </c>
+      <c r="W9" s="1">
+        <v>8</v>
+      </c>
+      <c r="X9" s="1">
+        <v>4</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:25 16375:16382">
@@ -1903,27 +1921,27 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="T15" s="2">
-        <f>T14+T6*5+T7</f>
+        <f t="shared" ref="T15:Y15" si="0">T14+T6*5+T7</f>
         <v>20000</v>
       </c>
       <c r="U15" s="2">
-        <f>U14+U6*5+U7</f>
+        <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="V15" s="2">
-        <f>V14+V6*5+V7</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="W15" s="2">
-        <f>W14+W6*5+W7</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="X15" s="2">
-        <f>X14+X6*5+X7</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="Y15" s="2">
-        <f>Y14+Y6*5+Y7</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="XEU15" s="1"/>
@@ -1976,31 +1994,31 @@
         <v>5011</v>
       </c>
       <c r="T16" s="2">
-        <f>T15+T7*5+T8</f>
+        <f t="shared" ref="T16:Y16" si="1">T15+T7*5+T8</f>
         <v>120000</v>
       </c>
       <c r="U16" s="2">
-        <f>U15+U7*5+U8</f>
-        <v>6500</v>
+        <f t="shared" si="1"/>
+        <v>6000</v>
       </c>
       <c r="V16" s="2">
-        <f>V15+V7*5+V8</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="W16" s="2">
-        <f>W15+W7*5+W8</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="X16" s="2">
-        <f>X15+X7*5+X8</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="Y16" s="2">
-        <f>Y15+Y7*5+Y8</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="3:15">
+    <row r="17" customHeight="1" spans="3:25">
       <c r="C17" s="1">
         <v>10</v>
       </c>
@@ -2040,8 +2058,32 @@
       <c r="O17" s="1">
         <v>5012</v>
       </c>
+      <c r="T17" s="2">
+        <f t="shared" ref="T17:Y17" si="2">T16+T8*5+T9</f>
+        <v>570000</v>
+      </c>
+      <c r="U17" s="2">
+        <f t="shared" si="2"/>
+        <v>28500</v>
+      </c>
+      <c r="V17" s="2">
+        <f t="shared" si="2"/>
+        <v>195</v>
+      </c>
+      <c r="W17" s="2">
+        <f t="shared" si="2"/>
+        <v>78</v>
+      </c>
+      <c r="X17" s="2">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="Y17" s="2">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
     </row>
-    <row r="18" customHeight="1" spans="3:15">
+    <row r="18" customHeight="1" spans="3:25">
       <c r="C18" s="1">
         <v>11</v>
       </c>
@@ -2082,7 +2124,7 @@
         <v>5013</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="3:15">
+    <row r="19" customHeight="1" spans="3:25">
       <c r="C19" s="1">
         <v>12</v>
       </c>
